--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/10_Segundo_Turno_Lula_vs_Renan_por_Sexo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/10_Segundo_Turno_Lula_vs_Renan_por_Sexo.xlsx
@@ -17,7 +17,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linhas_publicadas" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados_Mulheres'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo_Mulheres'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto_Mulheres'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Suavizados_Homens'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IC_Baixo_Homens'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IC_Alto_Homens'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cobertura'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metodologia'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Linhas_publicadas'!$A$1:$X$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +38,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +49,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -62,17 +81,35 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,54 +475,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>67.71356783919599</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>32.28643216080403</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>66.60020740890701</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>33.399792591093</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>66.21560973694521</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>33.78439026305479</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>64.89492538429917</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>35.10507461570083</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -496,54 +556,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>62.42259733837179</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>26.99546165997983</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>62.79458754833377</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>29.59417273051976</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>63.1105650880241</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>30.67934561413367</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>61.67027856307077</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>31.88042779447242</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -554,54 +637,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>73.00453834002018</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>37.57740266162822</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>70.40582726948026</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>37.20541245166623</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>69.32065438586632</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>36.8894349119759</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>68.11957220552758</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>38.32972143692923</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -612,54 +718,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>54.70737913486006</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>45.29262086513995</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>52.68950198511429</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>47.31049801488572</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>51.16581113804465</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>48.83418886195535</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>50.11123599996171</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>49.88876400003829</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -670,54 +799,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>49.07458155912231</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>39.6598232894022</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>48.65970332855776</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>43.28069935832919</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>47.88644763019702</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>45.55482535410772</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>46.73631996550733</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>46.51384796558391</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -728,54 +880,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Renan Santos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>60.3401767105978</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>50.92541844087771</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>56.71930064167082</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>51.34029667144225</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>54.44517464589227</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>52.11355236980297</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>53.48615203441609</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>53.26368003449267</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -786,33 +961,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
@@ -825,16 +1025,25 @@
       <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -846,19 +1055,29 @@
       <c r="B3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Futura, Nexus</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -869,16 +1088,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -890,7 +1113,7 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Brasil, 2º turno, estimulada, Lula × Renan Santos.</t>
         </is>
@@ -902,9 +1125,9 @@
           <t>Abertura</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grupos publicados de sexo; rótulos equivalentes são harmonizados conforme a aba Metodologia.</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Grupos publicados de sexo; somente rótulos equivalentes são harmonizados.</t>
         </is>
       </c>
     </row>
@@ -914,7 +1137,7 @@
           <t>Medida</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Lula e adversário convertidos para votos válidos dentro de cada grupo.</t>
         </is>
@@ -923,28 +1146,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica fallback conservador e isso não equivale à margem de erro total da pesquisa.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Exige ao menos dois grupos e duas datas publicadas em cada grupo desenhado.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é apenas amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral nem probabilidade de vitória.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -955,128 +1191,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>tipo_pesquisa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>frequencia_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>amostra_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>margem_erro_pp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nivel_confianca_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>turno</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>tipo_cenario</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>cenario</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>adversario</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>nivel_geografico</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>geografia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>segmento_tipo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>amostra_segmento</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>lula_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>adversario_pct</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>outros_candidatos_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>brancos_nulos_indecisos_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>base_voto</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>_linha_excel</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>peso_legacy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>grupo_abertura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1097,7 +1364,7 @@
       <c r="E2" t="n">
         <v>2000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
@@ -1146,13 +1413,13 @@
       <c r="Q2" t="n">
         <v>43</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="6" t="n">
         <v>35.6</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="6" t="n">
         <v>21.3</v>
       </c>
       <c r="U2" t="inlineStr">
@@ -1161,16 +1428,19 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="W2" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1191,7 +1461,7 @@
       <c r="E3" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
@@ -1237,16 +1507,16 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="6" t="n">
         <v>53.9</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="6" t="n">
         <v>25.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="6" t="n">
         <v>20.4</v>
       </c>
       <c r="U3" t="inlineStr">
@@ -1255,16 +1525,19 @@
         </is>
       </c>
       <c r="V3" t="n">
+        <v>1398</v>
+      </c>
+      <c r="W3" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1349,16 +1622,19 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>1572</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1443,16 +1719,19 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>1571</v>
+      </c>
+      <c r="W5" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1537,16 +1816,19 @@
         </is>
       </c>
       <c r="V6" t="n">
+        <v>1805</v>
+      </c>
+      <c r="W6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1631,16 +1913,19 @@
         </is>
       </c>
       <c r="V7" t="n">
+        <v>1804</v>
+      </c>
+      <c r="W7" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1725,16 +2010,19 @@
         </is>
       </c>
       <c r="V8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="W8" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1819,15 +2107,19 @@
         </is>
       </c>
       <c r="V9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="W9" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>